--- a/Templates/water-quality-analysis/Test_code/SSEMG_IS_20260223_label-table.xlsx
+++ b/Templates/water-quality-analysis/Test_code/SSEMG_IS_20260223_label-table.xlsx
@@ -377,7 +377,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SSEMG_R0030</t>
+          <t>SSEMG_R0035</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -385,16 +385,14 @@
           <t>SSEMG_STA_IS_20260223_1500</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+      <c r="C2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SSEMG_R0045</t>
+          <t>SSEMG_R0014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -402,16 +400,14 @@
           <t>SSEMG_STA_IS_20260223_1700</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+      <c r="C3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SSEMG_R0024</t>
+          <t>SSEMG_R0008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -419,16 +415,14 @@
           <t>SSEMG_STA_IS_20260223_1900</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="C4">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SSEMG_R0023</t>
+          <t>SSEMG_R0015</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -436,16 +430,14 @@
           <t>SSEMG_STA_IS_20260223_2100</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="C5">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SSEMG_R0016</t>
+          <t>SSEMG_R0048</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -453,16 +445,14 @@
           <t>SSEMG_STA_IS_20260223_2300</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+      <c r="C6">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SSEMG_R0009</t>
+          <t>SSEMG_R0026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -470,16 +460,14 @@
           <t>SSEMG_STA_IS_20260224_0100</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="C7">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SSEMG_R0025</t>
+          <t>SSEMG_R0031</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -487,16 +475,14 @@
           <t>SSEMG_STA_IS_20260224_0300</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="C8">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SSEMG_R0032</t>
+          <t>SSEMG_R0043</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -504,16 +490,14 @@
           <t>SSEMG_STA_IS_20260224_0500</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="C9">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SSEMG_R0041</t>
+          <t>SSEMG_R0018</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -521,16 +505,14 @@
           <t>SSEMG_STA_IS_20260224_0700</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+      <c r="C10">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SSEMG_R0036</t>
+          <t>SSEMG_R0042</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -538,16 +520,14 @@
           <t>SSEMG_STA_IS_20260224_0900</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C11">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SSEMG_R0040</t>
+          <t>SSEMG_R0039</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -555,16 +535,14 @@
           <t>SSEMG_STA_IS_20260224_1100</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C12">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SSEMG_R0018</t>
+          <t>SSEMG_R0027</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -572,16 +550,14 @@
           <t>SSEMG_STA_IS_20260224_1300</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C13">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SSEMG_R0014</t>
+          <t>SSEMG_R0047</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -589,16 +565,14 @@
           <t>SSEMG_STA_IS_20260224_1500</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C14">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SSEMG_R0035</t>
+          <t>SSEMG_R0024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -606,16 +580,14 @@
           <t>SSEMG_STA_IS_20260224_1700</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C15">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SSEMG_R0006</t>
+          <t>SSEMG_R0019</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -623,16 +595,14 @@
           <t>SSEMG_STA_IS_20260224_1900</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="C16">
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SSEMG_R0017</t>
+          <t>SSEMG_R0020</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -640,16 +610,14 @@
           <t>SSEMG_STA_IS_20260224_2100</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="C17">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SSEMG_R0046</t>
+          <t>SSEMG_R0021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -657,16 +625,14 @@
           <t>SSEMG_STA_IS_20260224_2300</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="C18">
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SSEMG_R0002</t>
+          <t>SSEMG_R0028</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -674,16 +640,14 @@
           <t>SSEMG_STA_IS_20260225_0100</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C19">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SSEMG_R0037</t>
+          <t>SSEMG_R0034</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -691,16 +655,14 @@
           <t>SSEMG_STA_IS_20260225_0300</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="C20">
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SSEMG_R0047</t>
+          <t>SSEMG_R0041</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -708,16 +670,14 @@
           <t>SSEMG_STA_IS_20260225_0500</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="C21">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SSEMG_R0031</t>
+          <t>SSEMG_R0022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -725,16 +685,14 @@
           <t>SSEMG_STA_IS_20260225_0700</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="C22">
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SSEMG_R0028</t>
+          <t>SSEMG_R0040</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -742,16 +700,14 @@
           <t>SSEMG_STA_IS_20260225_0900</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="C23">
+        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SSEMG_R0005</t>
+          <t>SSEMG_R0029</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -759,16 +715,14 @@
           <t>SSEMG_STA_IS_20260225_1100</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="C24">
+        <v>23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SSEMG_R0019</t>
+          <t>SSEMG_R0005</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -776,16 +730,14 @@
           <t>SSEMG_STA_IS_20260225_1300</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="C25">
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SSEMG_R0048</t>
+          <t>SSEMG_R0013</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -793,16 +745,14 @@
           <t>SSEMG_COA_IS_20260223_1700</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+      <c r="C26">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SSEMG_R0043</t>
+          <t>SSEMG_R0032</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -810,10 +760,8 @@
           <t>SSEMG_COA_IS_20260223_1900</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+      <c r="C27">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -827,16 +775,14 @@
           <t>SSEMG_COA_IS_20260223_2100</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="C28">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SSEMG_R0008</t>
+          <t>SSEMG_R0030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -844,16 +790,14 @@
           <t>SSEMG_COA_IS_20260223_2300</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="C29">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SSEMG_R0015</t>
+          <t>SSEMG_R0011</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -861,16 +805,14 @@
           <t>SSEMG_COA_IS_20260224_0100</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+      <c r="C30">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SSEMG_R0012</t>
+          <t>SSEMG_R0016</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -878,16 +820,14 @@
           <t>SSEMG_COA_IS_20260224_0300</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="C31">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SSEMG_R0029</t>
+          <t>SSEMG_R0033</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -895,16 +835,14 @@
           <t>SSEMG_COA_IS_20260224_0500</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="C32">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SSEMG_R0027</t>
+          <t>SSEMG_R0007</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -912,16 +850,14 @@
           <t>SSEMG_COA_IS_20260224_0700</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="C33">
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SSEMG_R0020</t>
+          <t>SSEMG_R0046</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -929,16 +865,14 @@
           <t>SSEMG_COA_IS_20260224_0900</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+      <c r="C34">
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SSEMG_R0033</t>
+          <t>SSEMG_R0002</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -946,16 +880,14 @@
           <t>SSEMG_COA_IS_20260224_1100</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C35">
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SSEMG_R0034</t>
+          <t>SSEMG_R0023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -963,16 +895,14 @@
           <t>SSEMG_COA_IS_20260224_1300</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C36">
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SSEMG_R0039</t>
+          <t>SSEMG_R0012</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -980,16 +910,14 @@
           <t>SSEMG_COA_IS_20260224_1500</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C37">
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SSEMG_R0011</t>
+          <t>SSEMG_R0004</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -997,16 +925,14 @@
           <t>SSEMG_COA_IS_20260224_1700</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C38">
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SSEMG_R0004</t>
+          <t>SSEMG_R0010</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1014,16 +940,14 @@
           <t>SSEMG_COA_IS_20260224_1900</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C39">
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SSEMG_R0007</t>
+          <t>SSEMG_R0038</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1031,16 +955,14 @@
           <t>SSEMG_COA_IS_20260224_2100</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="C40">
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SSEMG_R0001</t>
+          <t>SSEMG_R0003</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1048,16 +970,14 @@
           <t>SSEMG_COA_IS_20260224_2300</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="C41">
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SSEMG_R0038</t>
+          <t>SSEMG_R0036</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1065,16 +985,14 @@
           <t>SSEMG_COA_IS_20260225_0100</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="C42">
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SSEMG_R0013</t>
+          <t>SSEMG_R0009</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1082,16 +1000,14 @@
           <t>SSEMG_COA_IS_20260225_0300</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C43">
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SSEMG_R0022</t>
+          <t>SSEMG_R0025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1099,16 +1015,14 @@
           <t>SSEMG_COA_IS_20260225_0500</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="C44">
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SSEMG_R0042</t>
+          <t>SSEMG_R0037</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1116,16 +1030,14 @@
           <t>SSEMG_COA_IS_20260225_0700</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="C45">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SSEMG_R0021</t>
+          <t>SSEMG_R0017</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1133,16 +1045,14 @@
           <t>SSEMG_COA_IS_20260225_0900</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="C46">
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SSEMG_R0010</t>
+          <t>SSEMG_R0045</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1150,16 +1060,14 @@
           <t>SSEMG_COA_IS_20260225_1100</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="C47">
+        <v>22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SSEMG_R0003</t>
+          <t>SSEMG_R0001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1167,16 +1075,14 @@
           <t>SSEMG_COA_IS_20260225_1300</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="C48">
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SSEMG_R0026</t>
+          <t>SSEMG_R0006</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1184,10 +1090,8 @@
           <t>SSEMG_COA_IS_20260225_1500</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="C49">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1225,7 +1129,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2300_CN</t>
+          <t>SSEMG_COA_IS_20260225_1300_CN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1242,7 +1146,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2300_AQ</t>
+          <t>SSEMG_COA_IS_20260225_1300_AQ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1259,7 +1163,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2300_NU</t>
+          <t>SSEMG_COA_IS_20260225_1300_NU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1276,7 +1180,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2300_EX</t>
+          <t>SSEMG_COA_IS_20260225_1300_EX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1293,7 +1197,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2300_LV</t>
+          <t>SSEMG_COA_IS_20260225_1300_LV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1310,7 +1214,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0100_CN</t>
+          <t>SSEMG_COA_IS_20260224_1100_CN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1327,7 +1231,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0100_AQ</t>
+          <t>SSEMG_COA_IS_20260224_1100_AQ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1344,7 +1248,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0100_NU</t>
+          <t>SSEMG_COA_IS_20260224_1100_NU</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1361,7 +1265,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0100_EX</t>
+          <t>SSEMG_COA_IS_20260224_1100_EX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1378,7 +1282,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0100_LV</t>
+          <t>SSEMG_COA_IS_20260224_1100_LV</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1395,7 +1299,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1300_CN</t>
+          <t>SSEMG_COA_IS_20260224_2300_CN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1412,7 +1316,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1300_AQ</t>
+          <t>SSEMG_COA_IS_20260224_2300_AQ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1429,7 +1333,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1300_NU</t>
+          <t>SSEMG_COA_IS_20260224_2300_NU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1446,7 +1350,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1300_EX</t>
+          <t>SSEMG_COA_IS_20260224_2300_EX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1463,7 +1367,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1300_LV</t>
+          <t>SSEMG_COA_IS_20260224_2300_LV</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1480,7 +1384,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1900_CN</t>
+          <t>SSEMG_COA_IS_20260224_1700_CN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1497,7 +1401,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1900_AQ</t>
+          <t>SSEMG_COA_IS_20260224_1700_AQ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1514,7 +1418,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1900_NU</t>
+          <t>SSEMG_COA_IS_20260224_1700_NU</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1531,7 +1435,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1900_EX</t>
+          <t>SSEMG_COA_IS_20260224_1700_EX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1548,7 +1452,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1900_LV</t>
+          <t>SSEMG_COA_IS_20260224_1700_LV</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1565,7 +1469,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1100_CN</t>
+          <t>SSEMG_STA_IS_20260225_1300_CN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1582,7 +1486,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1100_AQ</t>
+          <t>SSEMG_STA_IS_20260225_1300_AQ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1599,7 +1503,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1100_NU</t>
+          <t>SSEMG_STA_IS_20260225_1300_NU</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1616,7 +1520,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1100_EX</t>
+          <t>SSEMG_STA_IS_20260225_1300_EX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1633,7 +1537,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1100_LV</t>
+          <t>SSEMG_STA_IS_20260225_1300_LV</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1650,7 +1554,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1900_CN</t>
+          <t>SSEMG_COA_IS_20260225_1500_CN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1667,7 +1571,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1900_AQ</t>
+          <t>SSEMG_COA_IS_20260225_1500_AQ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1684,7 +1588,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1900_NU</t>
+          <t>SSEMG_COA_IS_20260225_1500_NU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1701,7 +1605,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1900_EX</t>
+          <t>SSEMG_COA_IS_20260225_1500_EX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1718,7 +1622,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1900_LV</t>
+          <t>SSEMG_COA_IS_20260225_1500_LV</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1735,7 +1639,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2100_CN</t>
+          <t>SSEMG_COA_IS_20260224_0700_CN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1752,7 +1656,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2100_AQ</t>
+          <t>SSEMG_COA_IS_20260224_0700_AQ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1769,7 +1673,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2100_NU</t>
+          <t>SSEMG_COA_IS_20260224_0700_NU</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1786,7 +1690,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2100_EX</t>
+          <t>SSEMG_COA_IS_20260224_0700_EX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1803,7 +1707,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2100_LV</t>
+          <t>SSEMG_COA_IS_20260224_0700_LV</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1820,7 +1724,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_2300_CN</t>
+          <t>SSEMG_STA_IS_20260223_1900_CN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1837,7 +1741,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_2300_AQ</t>
+          <t>SSEMG_STA_IS_20260223_1900_AQ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1854,7 +1758,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_2300_NU</t>
+          <t>SSEMG_STA_IS_20260223_1900_NU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1871,7 +1775,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_2300_EX</t>
+          <t>SSEMG_STA_IS_20260223_1900_EX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1888,7 +1792,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_2300_LV</t>
+          <t>SSEMG_STA_IS_20260223_1900_LV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1905,7 +1809,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0100_CN</t>
+          <t>SSEMG_COA_IS_20260225_0300_CN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1922,7 +1826,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0100_AQ</t>
+          <t>SSEMG_COA_IS_20260225_0300_AQ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1939,7 +1843,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0100_NU</t>
+          <t>SSEMG_COA_IS_20260225_0300_NU</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1860,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0100_EX</t>
+          <t>SSEMG_COA_IS_20260225_0300_EX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1973,7 +1877,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0100_LV</t>
+          <t>SSEMG_COA_IS_20260225_0300_LV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1990,7 +1894,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1100_CN</t>
+          <t>SSEMG_COA_IS_20260224_1900_CN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2007,7 +1911,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1100_AQ</t>
+          <t>SSEMG_COA_IS_20260224_1900_AQ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2024,7 +1928,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1100_NU</t>
+          <t>SSEMG_COA_IS_20260224_1900_NU</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2041,7 +1945,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1100_EX</t>
+          <t>SSEMG_COA_IS_20260224_1900_EX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2058,7 +1962,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1100_LV</t>
+          <t>SSEMG_COA_IS_20260224_1900_LV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2075,7 +1979,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1700_CN</t>
+          <t>SSEMG_COA_IS_20260224_0100_CN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2092,7 +1996,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1700_AQ</t>
+          <t>SSEMG_COA_IS_20260224_0100_AQ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2109,7 +2013,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1700_NU</t>
+          <t>SSEMG_COA_IS_20260224_0100_NU</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2126,7 +2030,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1700_EX</t>
+          <t>SSEMG_COA_IS_20260224_0100_EX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2143,7 +2047,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1700_LV</t>
+          <t>SSEMG_COA_IS_20260224_0100_LV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2160,7 +2064,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0300_CN</t>
+          <t>SSEMG_COA_IS_20260224_1500_CN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2177,7 +2081,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0300_AQ</t>
+          <t>SSEMG_COA_IS_20260224_1500_AQ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2194,7 +2098,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0300_NU</t>
+          <t>SSEMG_COA_IS_20260224_1500_NU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2211,7 +2115,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0300_EX</t>
+          <t>SSEMG_COA_IS_20260224_1500_EX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2228,7 +2132,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0300_LV</t>
+          <t>SSEMG_COA_IS_20260224_1500_LV</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2245,7 +2149,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0300_CN</t>
+          <t>SSEMG_COA_IS_20260223_1700_CN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2262,7 +2166,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0300_AQ</t>
+          <t>SSEMG_COA_IS_20260223_1700_AQ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2279,7 +2183,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0300_NU</t>
+          <t>SSEMG_COA_IS_20260223_1700_NU</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2296,7 +2200,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0300_EX</t>
+          <t>SSEMG_COA_IS_20260223_1700_EX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2313,7 +2217,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0300_LV</t>
+          <t>SSEMG_COA_IS_20260223_1700_LV</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2330,7 +2234,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1500_CN</t>
+          <t>SSEMG_STA_IS_20260223_1700_CN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2347,7 +2251,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1500_AQ</t>
+          <t>SSEMG_STA_IS_20260223_1700_AQ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2364,7 +2268,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1500_NU</t>
+          <t>SSEMG_STA_IS_20260223_1700_NU</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2381,7 +2285,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1500_EX</t>
+          <t>SSEMG_STA_IS_20260223_1700_EX</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2398,7 +2302,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1500_LV</t>
+          <t>SSEMG_STA_IS_20260223_1700_LV</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2415,7 +2319,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0100_CN</t>
+          <t>SSEMG_STA_IS_20260223_2100_CN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2432,7 +2336,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0100_AQ</t>
+          <t>SSEMG_STA_IS_20260223_2100_AQ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2449,7 +2353,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0100_NU</t>
+          <t>SSEMG_STA_IS_20260223_2100_NU</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2466,7 +2370,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0100_EX</t>
+          <t>SSEMG_STA_IS_20260223_2100_EX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2483,7 +2387,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0100_LV</t>
+          <t>SSEMG_STA_IS_20260223_2100_LV</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2500,7 +2404,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2300_CN</t>
+          <t>SSEMG_COA_IS_20260224_0300_CN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2517,7 +2421,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2300_AQ</t>
+          <t>SSEMG_COA_IS_20260224_0300_AQ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2534,7 +2438,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2300_NU</t>
+          <t>SSEMG_COA_IS_20260224_0300_NU</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2551,7 +2455,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2300_EX</t>
+          <t>SSEMG_COA_IS_20260224_0300_EX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2568,7 +2472,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2300_LV</t>
+          <t>SSEMG_COA_IS_20260224_0300_LV</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2585,7 +2489,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2100_CN</t>
+          <t>SSEMG_COA_IS_20260225_0900_CN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2602,7 +2506,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2100_AQ</t>
+          <t>SSEMG_COA_IS_20260225_0900_AQ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2619,7 +2523,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2100_NU</t>
+          <t>SSEMG_COA_IS_20260225_0900_NU</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2636,7 +2540,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2100_EX</t>
+          <t>SSEMG_COA_IS_20260225_0900_EX</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2653,7 +2557,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2100_LV</t>
+          <t>SSEMG_COA_IS_20260225_0900_LV</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2670,7 +2574,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1300_CN</t>
+          <t>SSEMG_STA_IS_20260224_0700_CN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2687,7 +2591,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1300_AQ</t>
+          <t>SSEMG_STA_IS_20260224_0700_AQ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2704,7 +2608,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1300_NU</t>
+          <t>SSEMG_STA_IS_20260224_0700_NU</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2721,7 +2625,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1300_EX</t>
+          <t>SSEMG_STA_IS_20260224_0700_EX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2738,7 +2642,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1300_LV</t>
+          <t>SSEMG_STA_IS_20260224_0700_LV</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2755,7 +2659,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1300_CN</t>
+          <t>SSEMG_STA_IS_20260224_1900_CN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2772,7 +2676,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1300_AQ</t>
+          <t>SSEMG_STA_IS_20260224_1900_AQ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2789,7 +2693,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1300_NU</t>
+          <t>SSEMG_STA_IS_20260224_1900_NU</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2806,7 +2710,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1300_EX</t>
+          <t>SSEMG_STA_IS_20260224_1900_EX</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2823,7 +2727,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1300_LV</t>
+          <t>SSEMG_STA_IS_20260224_1900_LV</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2840,7 +2744,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0900_CN</t>
+          <t>SSEMG_STA_IS_20260224_2100_CN</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2857,7 +2761,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0900_AQ</t>
+          <t>SSEMG_STA_IS_20260224_2100_AQ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2874,7 +2778,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0900_NU</t>
+          <t>SSEMG_STA_IS_20260224_2100_NU</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2891,7 +2795,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0900_EX</t>
+          <t>SSEMG_STA_IS_20260224_2100_EX</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2908,7 +2812,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0900_LV</t>
+          <t>SSEMG_STA_IS_20260224_2100_LV</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2925,7 +2829,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0900_CN</t>
+          <t>SSEMG_STA_IS_20260224_2300_CN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2942,7 +2846,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0900_AQ</t>
+          <t>SSEMG_STA_IS_20260224_2300_AQ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2959,7 +2863,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0900_NU</t>
+          <t>SSEMG_STA_IS_20260224_2300_NU</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2976,7 +2880,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0900_EX</t>
+          <t>SSEMG_STA_IS_20260224_2300_EX</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2993,7 +2897,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0900_LV</t>
+          <t>SSEMG_STA_IS_20260224_2300_LV</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3010,7 +2914,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0500_CN</t>
+          <t>SSEMG_STA_IS_20260225_0700_CN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3027,7 +2931,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0500_AQ</t>
+          <t>SSEMG_STA_IS_20260225_0700_AQ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3044,7 +2948,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0500_NU</t>
+          <t>SSEMG_STA_IS_20260225_0700_NU</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3061,7 +2965,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0500_EX</t>
+          <t>SSEMG_STA_IS_20260225_0700_EX</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3078,7 +2982,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0500_LV</t>
+          <t>SSEMG_STA_IS_20260225_0700_LV</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3095,7 +2999,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2100_CN</t>
+          <t>SSEMG_COA_IS_20260224_1300_CN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3112,7 +3016,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2100_AQ</t>
+          <t>SSEMG_COA_IS_20260224_1300_AQ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3129,7 +3033,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2100_NU</t>
+          <t>SSEMG_COA_IS_20260224_1300_NU</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3146,7 +3050,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2100_EX</t>
+          <t>SSEMG_COA_IS_20260224_1300_EX</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3163,7 +3067,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2100_LV</t>
+          <t>SSEMG_COA_IS_20260224_1300_LV</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3180,7 +3084,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1900_CN</t>
+          <t>SSEMG_STA_IS_20260224_1700_CN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3197,7 +3101,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1900_AQ</t>
+          <t>SSEMG_STA_IS_20260224_1700_AQ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3214,7 +3118,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1900_NU</t>
+          <t>SSEMG_STA_IS_20260224_1700_NU</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3231,7 +3135,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1900_EX</t>
+          <t>SSEMG_STA_IS_20260224_1700_EX</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3248,7 +3152,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1900_LV</t>
+          <t>SSEMG_STA_IS_20260224_1700_LV</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3265,7 +3169,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0300_CN</t>
+          <t>SSEMG_COA_IS_20260225_0500_CN</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3282,7 +3186,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0300_AQ</t>
+          <t>SSEMG_COA_IS_20260225_0500_AQ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3299,7 +3203,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0300_NU</t>
+          <t>SSEMG_COA_IS_20260225_0500_NU</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3316,7 +3220,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0300_EX</t>
+          <t>SSEMG_COA_IS_20260225_0500_EX</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3333,7 +3237,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0300_LV</t>
+          <t>SSEMG_COA_IS_20260225_0500_LV</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3350,7 +3254,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1500_CN</t>
+          <t>SSEMG_STA_IS_20260224_0100_CN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3367,7 +3271,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1500_AQ</t>
+          <t>SSEMG_STA_IS_20260224_0100_AQ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3384,7 +3288,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1500_NU</t>
+          <t>SSEMG_STA_IS_20260224_0100_NU</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3401,7 +3305,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1500_EX</t>
+          <t>SSEMG_STA_IS_20260224_0100_EX</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3418,7 +3322,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1500_LV</t>
+          <t>SSEMG_STA_IS_20260224_0100_LV</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3435,7 +3339,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0700_CN</t>
+          <t>SSEMG_STA_IS_20260224_1300_CN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3452,7 +3356,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0700_AQ</t>
+          <t>SSEMG_STA_IS_20260224_1300_AQ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3469,7 +3373,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0700_NU</t>
+          <t>SSEMG_STA_IS_20260224_1300_NU</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3486,7 +3390,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0700_EX</t>
+          <t>SSEMG_STA_IS_20260224_1300_EX</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3503,7 +3407,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0700_LV</t>
+          <t>SSEMG_STA_IS_20260224_1300_LV</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3520,7 +3424,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0900_CN</t>
+          <t>SSEMG_STA_IS_20260225_0100_CN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3537,7 +3441,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0900_AQ</t>
+          <t>SSEMG_STA_IS_20260225_0100_AQ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3554,7 +3458,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0900_NU</t>
+          <t>SSEMG_STA_IS_20260225_0100_NU</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3571,7 +3475,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0900_EX</t>
+          <t>SSEMG_STA_IS_20260225_0100_EX</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3588,7 +3492,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0900_LV</t>
+          <t>SSEMG_STA_IS_20260225_0100_LV</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3605,7 +3509,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0500_CN</t>
+          <t>SSEMG_STA_IS_20260225_1100_CN</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3622,7 +3526,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0500_AQ</t>
+          <t>SSEMG_STA_IS_20260225_1100_AQ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3639,7 +3543,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0500_NU</t>
+          <t>SSEMG_STA_IS_20260225_1100_NU</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3656,7 +3560,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0500_EX</t>
+          <t>SSEMG_STA_IS_20260225_1100_EX</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3673,7 +3577,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0500_LV</t>
+          <t>SSEMG_STA_IS_20260225_1100_LV</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3690,7 +3594,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1500_CN</t>
+          <t>SSEMG_COA_IS_20260223_2300_CN</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3707,7 +3611,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1500_AQ</t>
+          <t>SSEMG_COA_IS_20260223_2300_AQ</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3724,7 +3628,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1500_NU</t>
+          <t>SSEMG_COA_IS_20260223_2300_NU</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3741,7 +3645,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1500_EX</t>
+          <t>SSEMG_COA_IS_20260223_2300_EX</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3758,7 +3662,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1500_LV</t>
+          <t>SSEMG_COA_IS_20260223_2300_LV</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3775,7 +3679,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0700_CN</t>
+          <t>SSEMG_STA_IS_20260224_0300_CN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3792,7 +3696,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0700_AQ</t>
+          <t>SSEMG_STA_IS_20260224_0300_AQ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3809,7 +3713,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0700_NU</t>
+          <t>SSEMG_STA_IS_20260224_0300_NU</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3826,7 +3730,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0700_EX</t>
+          <t>SSEMG_STA_IS_20260224_0300_EX</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3843,7 +3747,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0700_LV</t>
+          <t>SSEMG_STA_IS_20260224_0300_LV</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3860,7 +3764,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0500_CN</t>
+          <t>SSEMG_COA_IS_20260223_1900_CN</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3877,7 +3781,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0500_AQ</t>
+          <t>SSEMG_COA_IS_20260223_1900_AQ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3894,7 +3798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0500_NU</t>
+          <t>SSEMG_COA_IS_20260223_1900_NU</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3911,7 +3815,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0500_EX</t>
+          <t>SSEMG_COA_IS_20260223_1900_EX</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3928,7 +3832,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0500_LV</t>
+          <t>SSEMG_COA_IS_20260223_1900_LV</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3945,7 +3849,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1100_CN</t>
+          <t>SSEMG_COA_IS_20260224_0500_CN</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3962,7 +3866,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1100_AQ</t>
+          <t>SSEMG_COA_IS_20260224_0500_AQ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3979,7 +3883,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1100_NU</t>
+          <t>SSEMG_COA_IS_20260224_0500_NU</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3996,7 +3900,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1100_EX</t>
+          <t>SSEMG_COA_IS_20260224_0500_EX</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4013,7 +3917,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1100_LV</t>
+          <t>SSEMG_COA_IS_20260224_0500_LV</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4030,7 +3934,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1300_CN</t>
+          <t>SSEMG_STA_IS_20260225_0300_CN</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4047,7 +3951,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1300_AQ</t>
+          <t>SSEMG_STA_IS_20260225_0300_AQ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4064,7 +3968,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1300_NU</t>
+          <t>SSEMG_STA_IS_20260225_0300_NU</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4081,7 +3985,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1300_EX</t>
+          <t>SSEMG_STA_IS_20260225_0300_EX</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4098,7 +4002,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1300_LV</t>
+          <t>SSEMG_STA_IS_20260225_0300_LV</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4115,7 +4019,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1700_CN</t>
+          <t>SSEMG_STA_IS_20260223_1500_CN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4132,7 +4036,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1700_AQ</t>
+          <t>SSEMG_STA_IS_20260223_1500_AQ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4149,7 +4053,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1700_NU</t>
+          <t>SSEMG_STA_IS_20260223_1500_NU</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4166,7 +4070,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1700_EX</t>
+          <t>SSEMG_STA_IS_20260223_1500_EX</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4183,7 +4087,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1700_LV</t>
+          <t>SSEMG_STA_IS_20260223_1500_LV</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4200,7 +4104,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0900_CN</t>
+          <t>SSEMG_COA_IS_20260225_0100_CN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4217,7 +4121,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0900_AQ</t>
+          <t>SSEMG_COA_IS_20260225_0100_AQ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4234,7 +4138,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0900_NU</t>
+          <t>SSEMG_COA_IS_20260225_0100_NU</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4251,7 +4155,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0900_EX</t>
+          <t>SSEMG_COA_IS_20260225_0100_EX</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4268,7 +4172,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0900_LV</t>
+          <t>SSEMG_COA_IS_20260225_0100_LV</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4285,7 +4189,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0300_CN</t>
+          <t>SSEMG_COA_IS_20260225_0700_CN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4302,7 +4206,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0300_AQ</t>
+          <t>SSEMG_COA_IS_20260225_0700_AQ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4319,7 +4223,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0300_NU</t>
+          <t>SSEMG_COA_IS_20260225_0700_NU</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4336,7 +4240,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0300_EX</t>
+          <t>SSEMG_COA_IS_20260225_0700_EX</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4353,7 +4257,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0300_LV</t>
+          <t>SSEMG_COA_IS_20260225_0700_LV</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4370,7 +4274,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0100_CN</t>
+          <t>SSEMG_COA_IS_20260224_2100_CN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4387,7 +4291,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0100_AQ</t>
+          <t>SSEMG_COA_IS_20260224_2100_AQ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4404,7 +4308,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0100_NU</t>
+          <t>SSEMG_COA_IS_20260224_2100_NU</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4421,7 +4325,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0100_EX</t>
+          <t>SSEMG_COA_IS_20260224_2100_EX</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4438,7 +4342,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0100_LV</t>
+          <t>SSEMG_COA_IS_20260224_2100_LV</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4455,7 +4359,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1500_CN</t>
+          <t>SSEMG_STA_IS_20260224_1100_CN</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4472,7 +4376,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1500_AQ</t>
+          <t>SSEMG_STA_IS_20260224_1100_AQ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4489,7 +4393,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1500_NU</t>
+          <t>SSEMG_STA_IS_20260224_1100_NU</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4506,7 +4410,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1500_EX</t>
+          <t>SSEMG_STA_IS_20260224_1100_EX</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4523,7 +4427,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1500_LV</t>
+          <t>SSEMG_STA_IS_20260224_1100_LV</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4540,7 +4444,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1100_CN</t>
+          <t>SSEMG_STA_IS_20260225_0900_CN</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4557,7 +4461,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1100_AQ</t>
+          <t>SSEMG_STA_IS_20260225_0900_AQ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4574,7 +4478,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1100_NU</t>
+          <t>SSEMG_STA_IS_20260225_0900_NU</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4591,7 +4495,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1100_EX</t>
+          <t>SSEMG_STA_IS_20260225_0900_EX</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4608,7 +4512,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1100_LV</t>
+          <t>SSEMG_STA_IS_20260225_0900_LV</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4625,7 +4529,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0700_CN</t>
+          <t>SSEMG_STA_IS_20260225_0500_CN</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4642,7 +4546,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0700_AQ</t>
+          <t>SSEMG_STA_IS_20260225_0500_AQ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4659,7 +4563,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0700_NU</t>
+          <t>SSEMG_STA_IS_20260225_0500_NU</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4676,7 +4580,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0700_EX</t>
+          <t>SSEMG_STA_IS_20260225_0500_EX</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4693,7 +4597,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0700_LV</t>
+          <t>SSEMG_STA_IS_20260225_0500_LV</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4710,7 +4614,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0700_CN</t>
+          <t>SSEMG_STA_IS_20260224_0900_CN</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4727,7 +4631,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0700_AQ</t>
+          <t>SSEMG_STA_IS_20260224_0900_AQ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4744,7 +4648,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0700_NU</t>
+          <t>SSEMG_STA_IS_20260224_0900_NU</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4761,7 +4665,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0700_EX</t>
+          <t>SSEMG_STA_IS_20260224_0900_EX</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4778,7 +4682,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0700_LV</t>
+          <t>SSEMG_STA_IS_20260224_0900_LV</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4795,7 +4699,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1900_CN</t>
+          <t>SSEMG_STA_IS_20260224_0500_CN</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4812,7 +4716,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1900_AQ</t>
+          <t>SSEMG_STA_IS_20260224_0500_AQ</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4829,7 +4733,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1900_NU</t>
+          <t>SSEMG_STA_IS_20260224_0500_NU</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4846,7 +4750,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1900_EX</t>
+          <t>SSEMG_STA_IS_20260224_0500_EX</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4863,7 +4767,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1900_LV</t>
+          <t>SSEMG_STA_IS_20260224_0500_LV</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4965,7 +4869,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1700_CN</t>
+          <t>SSEMG_COA_IS_20260225_1100_CN</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4982,7 +4886,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1700_AQ</t>
+          <t>SSEMG_COA_IS_20260225_1100_AQ</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4999,7 +4903,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1700_NU</t>
+          <t>SSEMG_COA_IS_20260225_1100_NU</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5016,7 +4920,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1700_EX</t>
+          <t>SSEMG_COA_IS_20260225_1100_EX</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5033,7 +4937,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1700_LV</t>
+          <t>SSEMG_COA_IS_20260225_1100_LV</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5050,7 +4954,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2300_CN</t>
+          <t>SSEMG_COA_IS_20260224_0900_CN</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5067,7 +4971,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2300_AQ</t>
+          <t>SSEMG_COA_IS_20260224_0900_AQ</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5084,7 +4988,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2300_NU</t>
+          <t>SSEMG_COA_IS_20260224_0900_NU</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5101,7 +5005,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2300_EX</t>
+          <t>SSEMG_COA_IS_20260224_0900_EX</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5118,7 +5022,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2300_LV</t>
+          <t>SSEMG_COA_IS_20260224_0900_LV</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5135,7 +5039,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0500_CN</t>
+          <t>SSEMG_STA_IS_20260224_1500_CN</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5152,7 +5056,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0500_AQ</t>
+          <t>SSEMG_STA_IS_20260224_1500_AQ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5169,7 +5073,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0500_NU</t>
+          <t>SSEMG_STA_IS_20260224_1500_NU</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5186,7 +5090,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0500_EX</t>
+          <t>SSEMG_STA_IS_20260224_1500_EX</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5203,7 +5107,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0500_LV</t>
+          <t>SSEMG_STA_IS_20260224_1500_LV</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5220,7 +5124,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1700_CN</t>
+          <t>SSEMG_STA_IS_20260223_2300_CN</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5237,7 +5141,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1700_AQ</t>
+          <t>SSEMG_STA_IS_20260223_2300_AQ</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5254,7 +5158,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1700_NU</t>
+          <t>SSEMG_STA_IS_20260223_2300_NU</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5271,7 +5175,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1700_EX</t>
+          <t>SSEMG_STA_IS_20260223_2300_EX</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5288,7 +5192,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1700_LV</t>
+          <t>SSEMG_STA_IS_20260223_2300_LV</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5304,7 +5208,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5318,11 +5222,6 @@
           <t>field_sample_ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>botnum</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5332,12 +5231,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2300</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>SSEMG_COA_IS_20260225_1300</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5243,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0100</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>SSEMG_COA_IS_20260224_1100</t>
         </is>
       </c>
     </row>
@@ -5366,12 +5255,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1300</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>23</t>
+          <t>SSEMG_COA_IS_20260224_2300</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5267,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1900</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>SSEMG_COA_IS_20260224_1700</t>
         </is>
       </c>
     </row>
@@ -5400,12 +5279,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1100</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>23</t>
+          <t>SSEMG_STA_IS_20260225_1300</t>
         </is>
       </c>
     </row>
@@ -5417,12 +5291,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1900</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>SSEMG_COA_IS_20260225_1500</t>
         </is>
       </c>
     </row>
@@ -5434,12 +5303,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_2100</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>SSEMG_COA_IS_20260224_0700</t>
         </is>
       </c>
     </row>
@@ -5451,12 +5315,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_2300</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>04</t>
+          <t>SSEMG_STA_IS_20260223_1900</t>
         </is>
       </c>
     </row>
@@ -5468,12 +5327,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0100</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>06</t>
+          <t>SSEMG_COA_IS_20260225_0300</t>
         </is>
       </c>
     </row>
@@ -5485,12 +5339,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1100</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>22</t>
+          <t>SSEMG_COA_IS_20260224_1900</t>
         </is>
       </c>
     </row>
@@ -5502,12 +5351,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1700</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>SSEMG_COA_IS_20260224_0100</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5363,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0300</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>06</t>
+          <t>SSEMG_COA_IS_20260224_1500</t>
         </is>
       </c>
     </row>
@@ -5536,12 +5375,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0300</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>SSEMG_COA_IS_20260223_1700</t>
         </is>
       </c>
     </row>
@@ -5553,12 +5387,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1500</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>SSEMG_STA_IS_20260223_1700</t>
         </is>
       </c>
     </row>
@@ -5570,12 +5399,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0100</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>05</t>
+          <t>SSEMG_STA_IS_20260223_2100</t>
         </is>
       </c>
     </row>
@@ -5587,12 +5411,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2300</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>05</t>
+          <t>SSEMG_COA_IS_20260224_0300</t>
         </is>
       </c>
     </row>
@@ -5604,12 +5423,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2100</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>SSEMG_COA_IS_20260225_0900</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5435,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1300</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>SSEMG_STA_IS_20260224_0700</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5447,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_1300</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>SSEMG_STA_IS_20260224_1900</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5459,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0900</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>09</t>
+          <t>SSEMG_STA_IS_20260224_2100</t>
         </is>
       </c>
     </row>
@@ -5672,12 +5471,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0900</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>SSEMG_STA_IS_20260224_2300</t>
         </is>
       </c>
     </row>
@@ -5689,12 +5483,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0500</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>SSEMG_STA_IS_20260225_0700</t>
         </is>
       </c>
     </row>
@@ -5706,12 +5495,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_2100</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>04</t>
+          <t>SSEMG_COA_IS_20260224_1300</t>
         </is>
       </c>
     </row>
@@ -5723,12 +5507,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1900</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>03</t>
+          <t>SSEMG_STA_IS_20260224_1700</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5519,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0300</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>07</t>
+          <t>SSEMG_COA_IS_20260225_0500</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5531,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_1500</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>SSEMG_STA_IS_20260224_0100</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5543,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0700</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>08</t>
+          <t>SSEMG_STA_IS_20260224_1300</t>
         </is>
       </c>
     </row>
@@ -5791,12 +5555,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0900</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>22</t>
+          <t>SSEMG_STA_IS_20260225_0100</t>
         </is>
       </c>
     </row>
@@ -5808,12 +5567,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_0500</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>07</t>
+          <t>SSEMG_STA_IS_20260225_1100</t>
         </is>
       </c>
     </row>
@@ -5825,12 +5579,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1500</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>01</t>
+          <t>SSEMG_COA_IS_20260223_2300</t>
         </is>
       </c>
     </row>
@@ -5842,12 +5591,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0700</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>SSEMG_STA_IS_20260224_0300</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5603,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0500</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>08</t>
+          <t>SSEMG_COA_IS_20260223_1900</t>
         </is>
       </c>
     </row>
@@ -5876,12 +5615,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1100</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>SSEMG_COA_IS_20260224_0500</t>
         </is>
       </c>
     </row>
@@ -5893,12 +5627,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1300</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>SSEMG_STA_IS_20260225_0300</t>
         </is>
       </c>
     </row>
@@ -5910,12 +5639,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1700</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>SSEMG_STA_IS_20260223_1500</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5651,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0900</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>SSEMG_COA_IS_20260225_0100</t>
         </is>
       </c>
     </row>
@@ -5944,12 +5663,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0300</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>SSEMG_COA_IS_20260225_0700</t>
         </is>
       </c>
     </row>
@@ -5961,12 +5675,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0100</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>SSEMG_COA_IS_20260224_2100</t>
         </is>
       </c>
     </row>
@@ -5978,12 +5687,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260224_1500</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>SSEMG_STA_IS_20260224_1100</t>
         </is>
       </c>
     </row>
@@ -5995,12 +5699,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_1100</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>SSEMG_STA_IS_20260225_0900</t>
         </is>
       </c>
     </row>
@@ -6012,12 +5711,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_0700</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>09</t>
+          <t>SSEMG_STA_IS_20260225_0500</t>
         </is>
       </c>
     </row>
@@ -6029,12 +5723,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260225_0700</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>SSEMG_STA_IS_20260224_0900</t>
         </is>
       </c>
     </row>
@@ -6046,12 +5735,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1900</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>02</t>
+          <t>SSEMG_STA_IS_20260224_0500</t>
         </is>
       </c>
     </row>
@@ -6066,11 +5750,6 @@
           <t>SSEMG_COA_IS_20260223_2100</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6080,12 +5759,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260223_1700</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>02</t>
+          <t>SSEMG_COA_IS_20260225_1100</t>
         </is>
       </c>
     </row>
@@ -6097,12 +5771,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260224_2300</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>SSEMG_COA_IS_20260224_0900</t>
         </is>
       </c>
     </row>
@@ -6114,12 +5783,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_20260225_0500</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>SSEMG_STA_IS_20260224_1500</t>
         </is>
       </c>
     </row>
@@ -6131,12 +5795,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_20260223_1700</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>01</t>
+          <t>SSEMG_STA_IS_20260223_2300</t>
         </is>
       </c>
     </row>
@@ -6204,12 +5863,10 @@
         </is>
       </c>
       <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -6234,12 +5891,10 @@
         </is>
       </c>
       <c r="E3">
-        <v>45</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -6264,12 +5919,10 @@
         </is>
       </c>
       <c r="E4">
-        <v>24</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6294,12 +5947,10 @@
         </is>
       </c>
       <c r="E5">
-        <v>23</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6324,12 +5975,10 @@
         </is>
       </c>
       <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -6354,12 +6003,10 @@
         </is>
       </c>
       <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -6384,12 +6031,10 @@
         </is>
       </c>
       <c r="E8">
-        <v>25</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -6414,12 +6059,10 @@
         </is>
       </c>
       <c r="E9">
-        <v>32</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>43</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -6444,12 +6087,10 @@
         </is>
       </c>
       <c r="E10">
-        <v>41</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -6474,12 +6115,10 @@
         </is>
       </c>
       <c r="E11">
-        <v>36</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -6504,12 +6143,10 @@
         </is>
       </c>
       <c r="E12">
-        <v>40</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+        <v>39</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -6534,12 +6171,10 @@
         </is>
       </c>
       <c r="E13">
-        <v>18</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -6564,12 +6199,10 @@
         </is>
       </c>
       <c r="E14">
-        <v>14</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+        <v>47</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -6594,12 +6227,10 @@
         </is>
       </c>
       <c r="E15">
-        <v>35</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -6624,12 +6255,10 @@
         </is>
       </c>
       <c r="E16">
-        <v>6</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="F16">
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -6654,12 +6283,10 @@
         </is>
       </c>
       <c r="E17">
-        <v>17</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -6684,12 +6311,10 @@
         </is>
       </c>
       <c r="E18">
-        <v>46</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="F18">
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -6714,12 +6339,10 @@
         </is>
       </c>
       <c r="E19">
-        <v>2</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="F19">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -6744,12 +6367,10 @@
         </is>
       </c>
       <c r="E20">
-        <v>37</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="F20">
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -6774,12 +6395,10 @@
         </is>
       </c>
       <c r="E21">
-        <v>47</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+        <v>41</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -6804,12 +6423,10 @@
         </is>
       </c>
       <c r="E22">
-        <v>31</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="F22">
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -6834,12 +6451,10 @@
         </is>
       </c>
       <c r="E23">
-        <v>28</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="F23">
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -6864,12 +6479,10 @@
         </is>
       </c>
       <c r="E24">
-        <v>5</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="F24">
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -6894,12 +6507,10 @@
         </is>
       </c>
       <c r="E25">
-        <v>19</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="F25">
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -6924,12 +6535,10 @@
         </is>
       </c>
       <c r="E26">
-        <v>48</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -6954,12 +6563,10 @@
         </is>
       </c>
       <c r="E27">
-        <v>43</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -6986,10 +6593,8 @@
       <c r="E28">
         <v>44</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="F28">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -7014,12 +6619,10 @@
         </is>
       </c>
       <c r="E29">
-        <v>8</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -7044,12 +6647,10 @@
         </is>
       </c>
       <c r="E30">
-        <v>15</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -7074,12 +6675,10 @@
         </is>
       </c>
       <c r="E31">
-        <v>12</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="F31">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -7104,12 +6703,10 @@
         </is>
       </c>
       <c r="E32">
-        <v>29</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="F32">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -7134,12 +6731,10 @@
         </is>
       </c>
       <c r="E33">
-        <v>27</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -7164,12 +6759,10 @@
         </is>
       </c>
       <c r="E34">
-        <v>20</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+        <v>46</v>
+      </c>
+      <c r="F34">
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -7194,12 +6787,10 @@
         </is>
       </c>
       <c r="E35">
-        <v>33</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -7224,12 +6815,10 @@
         </is>
       </c>
       <c r="E36">
-        <v>34</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="F36">
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -7254,12 +6843,10 @@
         </is>
       </c>
       <c r="E37">
-        <v>39</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="F37">
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -7284,12 +6871,10 @@
         </is>
       </c>
       <c r="E38">
-        <v>11</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>13</v>
       </c>
     </row>
     <row r="39">
@@ -7314,12 +6899,10 @@
         </is>
       </c>
       <c r="E39">
-        <v>4</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>14</v>
       </c>
     </row>
     <row r="40">
@@ -7344,12 +6927,10 @@
         </is>
       </c>
       <c r="E40">
-        <v>7</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+        <v>38</v>
+      </c>
+      <c r="F40">
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -7374,12 +6955,10 @@
         </is>
       </c>
       <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -7404,12 +6983,10 @@
         </is>
       </c>
       <c r="E42">
-        <v>38</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="F42">
+        <v>17</v>
       </c>
     </row>
     <row r="43">
@@ -7434,12 +7011,10 @@
         </is>
       </c>
       <c r="E43">
-        <v>13</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="F43">
+        <v>18</v>
       </c>
     </row>
     <row r="44">
@@ -7464,12 +7039,10 @@
         </is>
       </c>
       <c r="E44">
-        <v>22</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="F44">
+        <v>19</v>
       </c>
     </row>
     <row r="45">
@@ -7494,12 +7067,10 @@
         </is>
       </c>
       <c r="E45">
-        <v>42</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+        <v>37</v>
+      </c>
+      <c r="F45">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -7524,12 +7095,10 @@
         </is>
       </c>
       <c r="E46">
+        <v>17</v>
+      </c>
+      <c r="F46">
         <v>21</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
       </c>
     </row>
     <row r="47">
@@ -7554,12 +7123,10 @@
         </is>
       </c>
       <c r="E47">
-        <v>10</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="F47">
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -7584,12 +7151,10 @@
         </is>
       </c>
       <c r="E48">
-        <v>3</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>23</v>
       </c>
     </row>
     <row r="49">
@@ -7614,12 +7179,10 @@
         </is>
       </c>
       <c r="E49">
-        <v>26</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="F49">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
